--- a/Sample_Dataset.xlsx
+++ b/Sample_Dataset.xlsx
@@ -8,10 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zuac-my.sharepoint.com/personal/z9959_zu_ac_ae/Documents/ZU/MyTools/ConduVet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="11_C82EBED3F62F5C47A81CC0ADAF09D1234568C4E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8007519F-39D4-6045-BBC9-38764258F9F5}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="11_C82EBED3F62F5C47A81CC0ADAF09D1234568C4E7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF706C0A-588B-4D4C-A780-411532C7F4C8}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="600" windowWidth="24420" windowHeight="15400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="11540" yWindow="13260" windowWidth="27640" windowHeight="9780" activeTab="1" xr2:uid="{AB150B8C-8CCF-7443-9992-24B9B61CD0C2}"/>
+    <workbookView xWindow="9260" yWindow="11820" windowWidth="27640" windowHeight="9780" xr2:uid="{AB150B8C-8CCF-7443-9992-24B9B61CD0C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -44,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
   <si>
     <t>Year</t>
   </si>
@@ -118,9 +117,6 @@
     <t>Old</t>
   </si>
   <si>
-    <t>Unvetted</t>
-  </si>
-  <si>
     <t>Depends on</t>
   </si>
   <si>
@@ -158,9 +154,6 @@
   </si>
   <si>
     <t>New</t>
-  </si>
-  <si>
-    <t>List (Unvetted, Vetted)</t>
   </si>
   <si>
     <t>Comments on the record data, status, etc.</t>
@@ -277,6 +270,12 @@
   </si>
   <si>
     <t>Research Type = BR</t>
+  </si>
+  <si>
+    <t>Vetted</t>
+  </si>
+  <si>
+    <t>Boolean</t>
   </si>
 </sst>
 </file>
@@ -437,7 +436,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -543,6 +542,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="9"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Comma 2" xfId="7" xr:uid="{35304157-9B47-4BAD-9B95-CD3D118939DF}"/>
@@ -903,10 +905,10 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H1" t="s">
         <v>20</v>
@@ -918,7 +920,7 @@
         <v>21</v>
       </c>
       <c r="K1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="L1" t="s">
         <v>22</v>
@@ -926,142 +928,142 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1">
         <v>2025</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
       </c>
       <c r="G2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" t="s">
-        <v>24</v>
+      <c r="K2" s="37" t="b">
+        <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C3" s="1">
         <v>2025</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
         <v>23</v>
       </c>
-      <c r="K3" t="s">
-        <v>24</v>
+      <c r="K3" s="37" t="b">
+        <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" t="s">
         <v>62</v>
       </c>
-      <c r="F4" t="s">
-        <v>64</v>
-      </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J4" t="s">
         <v>23</v>
       </c>
-      <c r="K4" t="s">
-        <v>24</v>
+      <c r="K4" s="37" t="b">
+        <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" s="1">
         <v>2025</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F5" t="s">
         <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J5" t="s">
         <v>23</v>
       </c>
-      <c r="K5" t="s">
-        <v>24</v>
+      <c r="K5" s="37" t="b">
+        <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1099,10 +1101,10 @@
         <v>9</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15">
@@ -1110,13 +1112,13 @@
         <v>19</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="D2" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="10" t="s">
@@ -1128,13 +1130,13 @@
         <v>18</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="9"/>
       <c r="F3" s="10" t="s">
@@ -1146,10 +1148,10 @@
         <v>0</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D4" s="21">
         <v>2026</v>
@@ -1188,7 +1190,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E6" s="9"/>
       <c r="F6" s="10" t="s">
@@ -1197,13 +1199,13 @@
     </row>
     <row r="7" spans="1:6" ht="314">
       <c r="A7" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" s="21" t="s">
         <v>4</v>
@@ -1215,19 +1217,19 @@
     </row>
     <row r="8" spans="1:6" ht="90">
       <c r="A8" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D8" s="21" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>10</v>
@@ -1238,13 +1240,13 @@
         <v>20</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" s="36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="10" t="s">
@@ -1256,13 +1258,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>35</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>36</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="17" t="s">
@@ -1277,10 +1279,10 @@
         <v>21</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="17" t="s">
@@ -1289,16 +1291,16 @@
     </row>
     <row r="12" spans="1:6" ht="15">
       <c r="A12" s="32" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>24</v>
+        <v>74</v>
+      </c>
+      <c r="D12" s="11" t="b">
+        <v>0</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="17" t="s">
@@ -1310,17 +1312,17 @@
         <v>22</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15">
@@ -1348,6 +1350,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003701CD0AA27D7E49B2EBD118B743C068" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="84adf66037c2e333f03cf0d6f2f5f5a5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f8c4534e-65bf-4e9b-a1f1-a352e3723734" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5fc83c9ee1c6d66abecc145708d93584" ns2:_="">
     <xsd:import namespace="f8c4534e-65bf-4e9b-a1f1-a352e3723734"/>
@@ -1509,12 +1517,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C141DD21-E081-4789-AEEA-FE9688CBD4B2}">
   <ds:schemaRefs>
@@ -1524,6 +1526,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2F51DE0-19D3-4CA2-9C91-F30FECDCB8B0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="f8c4534e-65bf-4e9b-a1f1-a352e3723734"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{236E80D6-6192-44DC-9EC0-2E66E766169B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1539,20 +1557,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2F51DE0-19D3-4CA2-9C91-F30FECDCB8B0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f8c4534e-65bf-4e9b-a1f1-a352e3723734"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>